--- a/Result/profitability/1418.xlsx
+++ b/Result/profitability/1418.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.47</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.115</v>
+        <v>-0.17375</v>
       </c>
       <c r="N2" t="n">
-        <v>11.76125</v>
+        <v>10.5075</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>-0.37</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1025</v>
+        <v>-0.47625</v>
       </c>
       <c r="N3" t="n">
-        <v>8.746250000000003</v>
+        <v>40.59125</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.9</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4712499999999999</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>38.945</v>
+        <v>38.5325</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.03</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5137499999999999</v>
+        <v>-0.5275</v>
       </c>
       <c r="N5" t="n">
-        <v>33.98375</v>
+        <v>33</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4124999999999999</v>
+        <v>-0.4412499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>33.145</v>
+        <v>21.68875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,28 +1264,28 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2625</v>
+        <v>-0.49875</v>
       </c>
       <c r="N7" t="n">
-        <v>22.51125</v>
+        <v>-2.53125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.99</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2575</v>
+        <v>-0.28125</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.141249999999999</v>
+        <v>0.9249999999999998</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.003749999999999976</v>
       </c>
       <c r="N9" t="n">
-        <v>1.161250000000001</v>
+        <v>1.16125</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.09750000000000003</v>
       </c>
       <c r="N10" t="n">
-        <v>3.222500000000001</v>
+        <v>3.2225</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.1712500000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>4.966250000000001</v>
+        <v>4.96625</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-745.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-31</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-51</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-51</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.17375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.5875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.1899999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2533333333333332</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-2.02078239608802</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1325301204819278</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.869999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4852034525277436</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
